--- a/Xlsx/Character.xlsx
+++ b/Xlsx/Character.xlsx
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="30">
   <si>
     <t>Id</t>
   </si>
   <si>
-    <t>SceneID</t>
+    <t>Type</t>
   </si>
   <si>
     <t>#Reamrk</t>
@@ -53,9 +53,6 @@
     <t>RelivePos</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>SubType</t>
   </si>
   <si>
@@ -71,7 +68,7 @@
     <t>Desc</t>
   </si>
   <si>
-    <t>无需配置</t>
+    <t>类型</t>
   </si>
   <si>
     <t>备注</t>
@@ -1169,7 +1166,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="15.0916666666667" customWidth="1"/>
-    <col min="2" max="4" width="16.0916666666667" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="3" max="4" width="16.0916666666667" customWidth="1"/>
     <col min="5" max="5" width="18.1833333333333" customWidth="1"/>
     <col min="6" max="6" width="21.45" customWidth="1"/>
     <col min="7" max="7" width="17.0916666666667" customWidth="1"/>
@@ -1205,80 +1203,80 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:11">
       <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="2" t="s">
         <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="5">
         <v>0</v>
@@ -1287,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
       </c>
       <c r="F4">
         <v>99999</v>
@@ -1299,7 +1297,7 @@
         <v>1000</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1313,19 +1311,17 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
       </c>
-      <c r="C5" s="5">
-        <v>0</v>
-      </c>
+      <c r="C5" s="5"/>
       <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
         <v>26</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
       </c>
       <c r="F5">
         <v>9999999</v>
@@ -1334,7 +1330,7 @@
         <v>1</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -1348,7 +1344,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="5">
         <v>0</v>
@@ -1357,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" t="s">
         <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
       </c>
       <c r="F6">
         <v>99999</v>
@@ -1369,7 +1365,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6">
         <v>2</v>
